--- a/Supplementary_data.xlsx
+++ b/Supplementary_data.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachelkirkland/Desktop/Rachel Kirkland/My_Project/Bi_gene_graphs/2025_recomb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AF6508-1FE2-C54A-BEE8-A1394BFE080F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C5F70-EE62-4F49-A100-B706EDA3A454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31400" yWindow="9940" windowWidth="23600" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supplementary Data1" sheetId="5" r:id="rId1"/>
     <sheet name="Supplementary Data2" sheetId="7" r:id="rId2"/>
+    <sheet name="Supplementary Data3" sheetId="8" r:id="rId3"/>
+    <sheet name="Supplementary Data4" sheetId="9" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
   <si>
     <t>nCells</t>
   </si>
@@ -225,10 +227,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3663(SmoM2);  8975(WT)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>6365(SmoM2);  6952(WT)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -237,10 +235,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>5199(Wls);  5572(WT)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>15625(Wls);  11243(WT)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -270,6 +264,88 @@
   </si>
   <si>
     <t>1346.646(Drop-seq); 294.8321(inDrops)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Module</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Within %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SmoM2-M1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SmoM2-M2</t>
+  </si>
+  <si>
+    <t>SmoM2-M3</t>
+  </si>
+  <si>
+    <t>Method</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>miloDE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LEMUR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total significant de genes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Module genes recovered</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50/73 (68.5%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>65/73 (89.0%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Within-module</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cross-module</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>One-in-module</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Module genes / total significant genes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supplementary Data3. Classification of DGCA significant differentially correlated gene pairs (18,642 total) by DiCoLo module membership in the SmoM2 dataset.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supplementary Data4. Recovery of DiCoLo SmoM2-specific module genes by miloDE and LEMUR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3663(SmoM2: 2568 LD + 997 UD + 98 DC);  8975(WT: 5846 LD + 3129 UD)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5199(Wls: 2092 LD + 3107 UD);  5572(WT: 1827 LD + 3545 UD + 200 DC)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -336,7 +412,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -352,6 +428,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,7 +785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="34">
+    <row r="3" spans="1:13" ht="85">
       <c r="A3" s="4" t="s">
         <v>23</v>
       </c>
@@ -754,13 +831,13 @@
         <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>44</v>
@@ -783,13 +860,13 @@
         <v>37</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>44</v>
@@ -812,13 +889,13 @@
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>45</v>
@@ -841,13 +918,13 @@
         <v>2</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>46</v>
@@ -1255,4 +1332,158 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C261F2D-90E5-9948-98E0-D6D8AC1ED858}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3">
+        <v>79</v>
+      </c>
+      <c r="C3">
+        <v>471</v>
+      </c>
+      <c r="D3">
+        <v>649</v>
+      </c>
+      <c r="E3">
+        <v>1199</v>
+      </c>
+      <c r="F3" s="7">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4">
+        <v>170</v>
+      </c>
+      <c r="C4">
+        <v>233</v>
+      </c>
+      <c r="D4">
+        <v>665</v>
+      </c>
+      <c r="E4">
+        <v>1068</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5">
+        <v>486</v>
+      </c>
+      <c r="C5">
+        <v>578</v>
+      </c>
+      <c r="D5">
+        <v>1655</v>
+      </c>
+      <c r="E5">
+        <v>2719</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.17899999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9EF7C8-7359-7944-9724-6D9E701B343D}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3">
+        <v>460</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.14130000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4">
+        <v>201</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.24879999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>